--- a/results/Int All Data.xlsx
+++ b/results/Int All Data.xlsx
@@ -878,52 +878,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82.55 ± 6.07</t>
+          <t>82.66 ± 5.73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>82.74 ± 6.18</t>
+          <t>82.87 ± 5.86</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>82.63 ± 6.20</t>
+          <t>82.75 ± 5.89</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>90.15 ± 6.67</t>
+          <t>90.22 ± 6.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>93.25 ± 4.58</t>
+          <t>93.31 ± 4.60</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>65.23 ± 12.28</t>
+          <t>65.48 ± 11.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>93.24 ± 4.58</t>
+          <t>93.31 ± 4.60</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16.60 ± 6.02</t>
+          <t>16.39 ± 6.09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>77.85 ± 12.54</t>
+          <t>78.53 ± 12.77</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>71.70 ± 13.06</t>
+          <t>72.98 ± 14.77</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1310,52 +1310,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82.22 ± 6.74</t>
+          <t>82.52 ± 6.31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>82.41 ± 6.92</t>
+          <t>82.72 ± 6.43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>82.31 ± 6.93</t>
+          <t>82.61 ± 6.45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>89.97 ± 6.81</t>
+          <t>90.04 ± 6.68</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>93.23 ± 4.60</t>
+          <t>93.23 ± 4.59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>64.60 ± 13.72</t>
+          <t>65.19 ± 12.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>93.23 ± 4.60</t>
+          <t>93.22 ± 4.59</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17.12 ± 6.73</t>
+          <t>17.18 ± 6.52</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>78.70 ± 11.89</t>
+          <t>78.69 ± 11.16</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>72.94 ± 12.82</t>
+          <t>73.16 ± 12.81</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1742,52 +1742,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.53 ± 5.87</t>
+          <t>82.76 ± 6.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>82.76 ± 6.05</t>
+          <t>82.92 ± 6.32</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>82.65 ± 6.07</t>
+          <t>82.82 ± 6.35</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>90.20 ± 6.68</t>
+          <t>89.71 ± 6.85</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>93.38 ± 4.59</t>
+          <t>93.02 ± 4.81</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>65.26 ± 11.96</t>
+          <t>65.64 ± 12.52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>93.38 ± 4.60</t>
+          <t>93.01 ± 4.81</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16.61 ± 6.17</t>
+          <t>17.10 ± 6.60</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>78.91 ± 11.92</t>
+          <t>77.15 ± 13.84</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>73.21 ± 14.24</t>
+          <t>72.05 ± 14.43</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2174,52 +2174,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.75 ± 5.70</t>
+          <t>82.66 ± 5.52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>82.94 ± 5.89</t>
+          <t>82.86 ± 5.71</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>82.83 ± 5.91</t>
+          <t>82.75 ± 5.74</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>90.40 ± 6.28</t>
+          <t>90.24 ± 6.89</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>93.49 ± 4.31</t>
+          <t>93.33 ± 4.72</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>65.66 ± 11.64</t>
+          <t>65.49 ± 11.28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>93.49 ± 4.31</t>
+          <t>93.32 ± 4.72</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>16.46 ± 5.95</t>
+          <t>16.65 ± 6.06</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>78.64 ± 11.55</t>
+          <t>78.51 ± 12.47</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>73.65 ± 13.26</t>
+          <t>72.70 ± 14.53</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2606,52 +2606,52 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.73 ± 6.45</t>
+          <t>82.55 ± 6.92</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>82.87 ± 6.60</t>
+          <t>82.71 ± 7.08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>82.78 ± 6.62</t>
+          <t>82.62 ± 7.10</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>90.35 ± 6.45</t>
+          <t>90.16 ± 6.85</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>93.42 ± 4.48</t>
+          <t>93.34 ± 4.67</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>65.55 ± 13.06</t>
+          <t>65.22 ± 14.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>93.42 ± 4.48</t>
+          <t>93.33 ± 4.67</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>16.42 ± 6.29</t>
+          <t>17.20 ± 6.80</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>78.78 ± 11.86</t>
+          <t>78.66 ± 11.77</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>72.64 ± 13.47</t>
+          <t>72.46 ± 13.49</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3038,52 +3038,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.73 ± 4.88</t>
+          <t>82.28 ± 3.97</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>82.80 ± 5.02</t>
+          <t>82.39 ± 4.10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>82.73 ± 5.02</t>
+          <t>82.31 ± 4.09</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>90.40 ± 4.60</t>
+          <t>90.30 ± 4.59</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>93.31 ± 2.94</t>
+          <t>93.22 ± 2.89</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>65.46 ± 9.93</t>
+          <t>64.60 ± 8.08</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>93.31 ± 2.94</t>
+          <t>93.22 ± 2.89</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>17.34 ± 5.54</t>
+          <t>17.91 ± 5.33</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>77.36 ± 8.73</t>
+          <t>77.03 ± 8.02</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>72.18 ± 7.36</t>
+          <t>72.65 ± 7.37</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3470,52 +3470,52 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.36 ± 5.90</t>
+          <t>83.20 ± 6.77</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>83.33 ± 6.05</t>
+          <t>83.17 ± 6.91</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>83.29 ± 6.07</t>
+          <t>83.12 ± 6.94</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>90.16 ± 6.19</t>
+          <t>90.15 ± 6.30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>93.24 ± 3.98</t>
+          <t>93.26 ± 4.08</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>66.63 ± 12.01</t>
+          <t>66.30 ± 13.73</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>93.23 ± 3.99</t>
+          <t>93.25 ± 4.08</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>16.45 ± 5.95</t>
+          <t>16.20 ± 6.17</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>79.53 ± 10.63</t>
+          <t>79.54 ± 11.58</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>73.41 ± 12.20</t>
+          <t>72.78 ± 11.88</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3902,52 +3902,52 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>82.85 ± 7.04</t>
+          <t>82.93 ± 7.31</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>82.83 ± 7.12</t>
+          <t>82.89 ± 7.37</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>82.77 ± 7.17</t>
+          <t>82.84 ± 7.42</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>88.84 ± 7.84</t>
+          <t>88.90 ± 7.78</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>92.10 ± 5.24</t>
+          <t>92.13 ± 5.28</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>65.65 ± 14.13</t>
+          <t>65.79 ± 14.64</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>92.09 ± 5.25</t>
+          <t>92.13 ± 5.28</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>18.19 ± 7.87</t>
+          <t>17.89 ± 7.88</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>76.63 ± 14.16</t>
+          <t>76.58 ± 13.93</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>71.89 ± 13.16</t>
+          <t>71.87 ± 13.48</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4334,52 +4334,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>82.85 ± 5.17</t>
+          <t>83.02 ± 4.40</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>82.64 ± 5.20</t>
+          <t>82.81 ± 4.43</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>82.54 ± 5.25</t>
+          <t>82.70 ± 4.48</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>90.09 ± 5.67</t>
+          <t>89.99 ± 5.81</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>92.83 ± 3.77</t>
+          <t>92.87 ± 3.65</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>65.41 ± 10.36</t>
+          <t>65.74 ± 8.84</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>92.83 ± 3.77</t>
+          <t>92.86 ± 3.65</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>16.35 ± 6.04</t>
+          <t>16.74 ± 5.65</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>78.83 ± 10.65</t>
+          <t>79.10 ± 9.02</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>73.41 ± 11.31</t>
+          <t>73.46 ± 11.58</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4766,52 +4766,52 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>84.73 ± 7.98</t>
+          <t>84.17 ± 7.46</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>85.06 ± 7.78</t>
+          <t>84.48 ± 7.28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>84.76 ± 8.04</t>
+          <t>84.19 ± 7.50</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>92.06 ± 6.55</t>
+          <t>92.00 ± 6.09</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>93.31 ± 5.48</t>
+          <t>93.18 ± 5.22</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>69.76 ± 15.83</t>
+          <t>68.62 ± 14.81</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>93.30 ± 5.48</t>
+          <t>93.18 ± 5.23</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>14.45 ± 8.41</t>
+          <t>15.04 ± 8.56</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>82.01 ± 13.50</t>
+          <t>81.68 ± 13.56</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>78.10 ± 14.46</t>
+          <t>75.77 ± 14.27</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -5198,52 +5198,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>84.53 ± 6.85</t>
+          <t>83.67 ± 7.42</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>84.59 ± 6.73</t>
+          <t>83.72 ± 7.35</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>84.41 ± 6.87</t>
+          <t>83.50 ± 7.52</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>91.91 ± 6.25</t>
+          <t>91.48 ± 6.35</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>93.25 ± 4.62</t>
+          <t>93.00 ± 4.56</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>69.01 ± 13.54</t>
+          <t>67.28 ± 14.76</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>93.24 ± 4.62</t>
+          <t>92.99 ± 4.57</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>14.99 ± 8.04</t>
+          <t>15.53 ± 7.55</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>81.50 ± 12.60</t>
+          <t>80.23 ± 11.78</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>76.48 ± 14.62</t>
+          <t>75.07 ± 13.67</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5630,52 +5630,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>83.37 ± 6.77</t>
+          <t>83.29 ± 6.68</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>84.12 ± 6.21</t>
+          <t>84.00 ± 5.91</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>83.74 ± 6.70</t>
+          <t>83.66 ± 6.39</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>91.94 ± 7.94</t>
+          <t>91.98 ± 7.66</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>91.87 ± 7.40</t>
+          <t>91.65 ± 7.57</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>67.04 ± 13.26</t>
+          <t>66.76 ± 12.76</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>91.87 ± 7.40</t>
+          <t>91.65 ± 7.57</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>14.75 ± 8.69</t>
+          <t>15.48 ± 8.98</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>79.19 ± 14.55</t>
+          <t>78.95 ± 15.17</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>73.91 ± 16.63</t>
+          <t>73.27 ± 17.32</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -6062,52 +6062,52 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>84.32 ± 6.29</t>
+          <t>84.00 ± 6.54</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>85.75 ± 5.18</t>
+          <t>85.29 ± 5.49</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>85.54 ± 5.47</t>
+          <t>85.10 ± 5.76</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>91.01 ± 8.68</t>
+          <t>90.80 ± 8.83</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>90.46 ± 7.67</t>
+          <t>90.26 ± 7.72</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>69.24 ± 11.72</t>
+          <t>68.38 ± 12.27</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>90.46 ± 7.66</t>
+          <t>90.25 ± 7.72</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>16.50 ± 9.67</t>
+          <t>17.03 ± 8.68</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>79.91 ± 14.00</t>
+          <t>77.97 ± 13.43</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>73.31 ± 14.02</t>
+          <t>72.89 ± 13.79</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -6494,52 +6494,52 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>83.55 ± 7.74</t>
+          <t>84.43 ± 7.89</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>84.96 ± 6.14</t>
+          <t>85.97 ± 6.34</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>84.51 ± 6.94</t>
+          <t>85.49 ± 7.18</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>91.13 ± 10.08</t>
+          <t>90.83 ± 10.56</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>89.45 ± 10.47</t>
+          <t>89.45 ± 10.80</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>67.05 ± 14.67</t>
+          <t>69.12 ± 14.97</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>89.45 ± 10.47</t>
+          <t>89.44 ± 10.81</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>15.41 ± 9.64</t>
+          <t>15.86 ± 10.08</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>78.67 ± 17.57</t>
+          <t>77.75 ± 17.62</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>71.51 ± 16.71</t>
+          <t>73.31 ± 16.55</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6926,52 +6926,52 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>82.57 ± 7.53</t>
+          <t>83.09 ± 8.08</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>86.35 ± 4.63</t>
+          <t>86.45 ± 5.16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>85.80 ± 5.10</t>
+          <t>85.95 ± 5.67</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>90.05 ± 9.69</t>
+          <t>90.39 ± 9.56</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>87.95 ± 9.57</t>
+          <t>88.32 ± 9.73</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>66.69 ± 11.81</t>
+          <t>67.13 ± 13.24</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>87.92 ± 9.62</t>
+          <t>88.31 ± 9.72</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>17.64 ± 9.61</t>
+          <t>16.40 ± 10.74</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>78.58 ± 14.25</t>
+          <t>79.31 ± 16.29</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>73.88 ± 13.43</t>
+          <t>75.79 ± 16.72</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -7358,52 +7358,52 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>82.22 ± 11.09</t>
+          <t>82.37 ± 10.89</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>87.43 ± 7.41</t>
+          <t>87.72 ± 7.22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>87.00 ± 7.75</t>
+          <t>87.27 ± 7.53</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>89.06 ± 13.51</t>
+          <t>89.38 ± 12.97</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>85.42 ± 15.57</t>
+          <t>85.59 ± 15.22</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>66.03 ± 20.86</t>
+          <t>66.64 ± 20.29</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>85.36 ± 15.65</t>
+          <t>85.57 ± 15.25</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>18.27 ± 15.20</t>
+          <t>17.54 ± 14.48</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>77.98 ± 22.08</t>
+          <t>78.61 ± 21.86</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>75.29 ± 21.60</t>
+          <t>73.93 ± 21.64</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -7790,52 +7790,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>82.41 ± 12.64</t>
+          <t>82.55 ± 13.16</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>89.59 ± 6.30</t>
+          <t>89.83 ± 6.68</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>88.61 ± 7.77</t>
+          <t>88.83 ± 8.20</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>86.38 ± 17.71</t>
+          <t>87.57 ± 15.99</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>81.34 ± 20.54</t>
+          <t>81.47 ± 20.27</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>66.82 ± 23.71</t>
+          <t>67.41 ± 24.98</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>81.24 ± 20.78</t>
+          <t>81.39 ± 20.44</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>20.59 ± 17.01</t>
+          <t>20.38 ± 16.40</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>75.60 ± 23.93</t>
+          <t>75.40 ± 23.78</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>70.01 ± 23.33</t>
+          <t>68.89 ± 24.58</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -8222,52 +8222,52 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>85.30 ± 15.09</t>
+          <t>85.79 ± 13.47</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>92.69 ± 6.19</t>
+          <t>92.58 ± 6.34</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>91.76 ± 8.15</t>
+          <t>91.90 ± 7.73</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>91.15 ± 18.46</t>
+          <t>91.63 ± 17.36</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>85.78 ± 23.17</t>
+          <t>86.42 ± 21.64</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>71.17 ± 28.52</t>
+          <t>72.27 ± 25.76</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>85.48 ± 23.89</t>
+          <t>86.21 ± 22.15</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>12.21 ± 18.45</t>
+          <t>11.85 ± 17.44</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>82.44 ± 28.61</t>
+          <t>84.62 ± 26.07</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>79.92 ± 31.09</t>
+          <t>81.54 ± 28.79</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -8654,52 +8654,52 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>87.07 ± 14.74</t>
+          <t>86.87 ± 15.74</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>93.62 ± 7.64</t>
+          <t>93.74 ± 7.87</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>93.03 ± 8.81</t>
+          <t>93.15 ± 9.00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>90.04 ± 19.37</t>
+          <t>90.16 ± 19.12</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>85.10 ± 24.21</t>
+          <t>85.40 ± 24.21</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.13 ± 29.49</t>
+          <t>76.15 ± 31.38</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>84.82 ± 24.86</t>
+          <t>85.13 ± 24.81</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>13.87 ± 19.77</t>
+          <t>13.33 ± 19.37</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>82.40 ± 29.48</t>
+          <t>82.27 ± 30.39</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>79.28 ± 30.96</t>
+          <t>80.43 ± 30.97</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -9086,52 +9086,52 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>84.66 ± 15.08</t>
+          <t>86.43 ± 14.26</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>93.14 ± 7.43</t>
+          <t>93.96 ± 6.49</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>92.43 ± 8.64</t>
+          <t>93.24 ± 7.94</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>90.76 ± 18.22</t>
+          <t>91.19 ± 18.30</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>83.20 ± 23.22</t>
+          <t>84.82 ± 23.10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>72.04 ± 29.31</t>
+          <t>75.10 ± 26.88</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>82.80 ± 24.00</t>
+          <t>84.47 ± 23.81</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>13.47 ± 20.08</t>
+          <t>12.92 ± 20.46</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>82.33 ± 29.58</t>
+          <t>84.64 ± 28.11</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>79.87 ± 31.33</t>
+          <t>80.88 ± 31.06</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -9518,52 +9518,52 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>85.49 ± 15.17</t>
+          <t>85.00 ± 14.45</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>93.62 ± 6.50</t>
+          <t>93.64 ± 6.15</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>92.73 ± 8.15</t>
+          <t>92.77 ± 7.72</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>91.05 ± 16.41</t>
+          <t>92.05 ± 15.29</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>74.33 ± 31.42</t>
+          <t>76.16 ± 30.93</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>62.94 ± 34.26</t>
+          <t>62.80 ± 32.75</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>78.99 ± 22.23</t>
+          <t>81.03 ± 20.70</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>22.33 ± 30.62</t>
+          <t>21.59 ± 30.23</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>83.15 ± 23.37</t>
+          <t>84.76 ± 22.43</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>74.97 ± 26.91</t>
+          <t>79.08 ± 24.11</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
